--- a/Data/EXCEL/Transfer/salemon/202412/5281-salemon-202412.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202412/5281-salemon-202412.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WORKSPACES\xls2xlsx\202412\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WORKSPACES\xls2xlsx\Transfer\202412\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D58B58A1-4149-4CD8-9572-326145EFFBA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{422CE696-53F2-41A6-B7BD-C22C065747D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="17500" xr2:uid="{8F0FFE60-54DF-43A2-A173-AA4A6488A4A0}"/>
+    <workbookView xWindow="2235" yWindow="1695" windowWidth="21600" windowHeight="13425" xr2:uid="{F681DF86-FB22-41A4-88F7-D495990C071B}"/>
   </bookViews>
   <sheets>
     <sheet name="5281-salemon-202412" sheetId="2" r:id="rId1"/>
@@ -1255,24 +1255,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEF3EA65-1662-4373-8606-3FF7FF9074A7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B02B10DD-2251-44E7-88C0-E30E29F51FA6}">
   <dimension ref="A1:Q29"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.81640625" customWidth="1"/>
-    <col min="2" max="5" width="14.54296875" customWidth="1"/>
-    <col min="6" max="6" width="13.81640625" customWidth="1"/>
-    <col min="7" max="9" width="14.54296875" customWidth="1"/>
-    <col min="10" max="10" width="13.81640625" customWidth="1"/>
-    <col min="11" max="11" width="14.54296875" customWidth="1"/>
-    <col min="12" max="12" width="13.81640625" customWidth="1"/>
-    <col min="13" max="14" width="14.54296875" customWidth="1"/>
-    <col min="15" max="15" width="13.81640625" customWidth="1"/>
-    <col min="16" max="16" width="14.54296875" customWidth="1"/>
-    <col min="17" max="17" width="15" customWidth="1"/>
+    <col min="1" max="1" width="11.875" customWidth="1"/>
+    <col min="2" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="9.5" customWidth="1"/>
+    <col min="7" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="9.5" customWidth="1"/>
+    <col min="11" max="11" width="10" customWidth="1"/>
+    <col min="12" max="12" width="9.5" customWidth="1"/>
+    <col min="13" max="14" width="10" customWidth="1"/>
+    <col min="15" max="15" width="9.5" customWidth="1"/>
+    <col min="16" max="16" width="10" customWidth="1"/>
+    <col min="17" max="17" width="10.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
@@ -1299,7 +1299,7 @@
       <c r="P1" s="20"/>
       <c r="Q1" s="21"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="17"/>
       <c r="B2" s="16" t="s">
         <v>4</v>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="Q2" s="21"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="17"/>
       <c r="B3" s="17"/>
       <c r="C3" s="17"/>
@@ -1381,7 +1381,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="18"/>
       <c r="B4" s="18"/>
       <c r="C4" s="18"/>
@@ -1420,7 +1420,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>45170</v>
       </c>
@@ -1473,7 +1473,7 @@
         <v>-10.6</v>
       </c>
     </row>
-    <row r="6" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="11">
         <v>45139</v>
       </c>
@@ -1526,7 +1526,7 @@
         <v>-12.6</v>
       </c>
     </row>
-    <row r="7" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>45108</v>
       </c>
@@ -1579,7 +1579,7 @@
         <v>-10.3</v>
       </c>
     </row>
-    <row r="8" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="11">
         <v>45078</v>
       </c>
@@ -1632,7 +1632,7 @@
         <v>-12.3</v>
       </c>
     </row>
-    <row r="9" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>45047</v>
       </c>
@@ -1685,7 +1685,7 @@
         <v>-8.7200000000000006</v>
       </c>
     </row>
-    <row r="10" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="11">
         <v>45017</v>
       </c>
@@ -1738,7 +1738,7 @@
         <v>-15.6</v>
       </c>
     </row>
-    <row r="11" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>44986</v>
       </c>
@@ -1791,7 +1791,7 @@
         <v>-25.6</v>
       </c>
     </row>
-    <row r="12" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="11">
         <v>44958</v>
       </c>
@@ -1844,7 +1844,7 @@
         <v>-38.9</v>
       </c>
     </row>
-    <row r="13" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
         <v>44927</v>
       </c>
@@ -1897,7 +1897,7 @@
         <v>-79.900000000000006</v>
       </c>
     </row>
-    <row r="14" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="11">
         <v>44896</v>
       </c>
@@ -1950,7 +1950,7 @@
         <v>-39.1</v>
       </c>
     </row>
-    <row r="15" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
         <v>44866</v>
       </c>
@@ -2003,7 +2003,7 @@
         <v>-39.4</v>
       </c>
     </row>
-    <row r="16" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="11">
         <v>44835</v>
       </c>
@@ -2056,7 +2056,7 @@
         <v>-40.299999999999997</v>
       </c>
     </row>
-    <row r="17" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
         <v>44805</v>
       </c>
@@ -2109,7 +2109,7 @@
         <v>-39.200000000000003</v>
       </c>
     </row>
-    <row r="18" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="11">
         <v>44774</v>
       </c>
@@ -2162,7 +2162,7 @@
         <v>-37.4</v>
       </c>
     </row>
-    <row r="19" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
         <v>44743</v>
       </c>
@@ -2215,7 +2215,7 @@
         <v>-38.700000000000003</v>
       </c>
     </row>
-    <row r="20" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="11">
         <v>44713</v>
       </c>
@@ -2268,7 +2268,7 @@
         <v>-41.8</v>
       </c>
     </row>
-    <row r="21" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
         <v>44682</v>
       </c>
@@ -2321,7 +2321,7 @@
         <v>-35.9</v>
       </c>
     </row>
-    <row r="22" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="11">
         <v>44652</v>
       </c>
@@ -2374,7 +2374,7 @@
         <v>-35.799999999999997</v>
       </c>
     </row>
-    <row r="23" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
         <v>44621</v>
       </c>
@@ -2427,7 +2427,7 @@
         <v>-21.8</v>
       </c>
     </row>
-    <row r="24" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="11">
         <v>44593</v>
       </c>
@@ -2480,7 +2480,7 @@
         <v>-35.700000000000003</v>
       </c>
     </row>
-    <row r="25" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
         <v>44562</v>
       </c>
@@ -2533,7 +2533,7 @@
         <v>-49.6</v>
       </c>
     </row>
-    <row r="26" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="11">
         <v>44531</v>
       </c>
@@ -2586,7 +2586,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="27" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
         <v>44501</v>
       </c>
@@ -2639,7 +2639,7 @@
         <v>18.3</v>
       </c>
     </row>
-    <row r="28" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="11">
         <v>44470</v>
       </c>
@@ -2692,7 +2692,7 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="29" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
         <v>44440</v>
       </c>
